--- a/sample_data/output/excel/03_주택종류별_집계.xlsx
+++ b/sample_data/output/excel/03_주택종류별_집계.xlsx
@@ -473,19 +473,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>1696</v>
       </c>
       <c r="E2" t="n">
-        <v>3372.4663</v>
+        <v>1310952.632067373</v>
       </c>
       <c r="F2" t="n">
-        <v>78986.42857142857</v>
+        <v>38421.9204009434</v>
       </c>
       <c r="G2" t="n">
-        <v>76083.71428571429</v>
+        <v>15548.62617924528</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.04952830188679246</v>
       </c>
     </row>
     <row r="3">
@@ -503,19 +503,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>47</v>
+        <v>1779</v>
       </c>
       <c r="E3" t="n">
-        <v>7696.1155</v>
+        <v>1251568.392007142</v>
       </c>
       <c r="F3" t="n">
-        <v>79048.76595744681</v>
+        <v>24391.32827431141</v>
       </c>
       <c r="G3" t="n">
-        <v>78254.36170212766</v>
+        <v>11724.16020236088</v>
       </c>
       <c r="H3" t="n">
-        <v>0.148936170212766</v>
+        <v>0.09499718943226532</v>
       </c>
     </row>
     <row r="4">
@@ -533,19 +533,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>82</v>
+        <v>1377</v>
       </c>
       <c r="E4" t="n">
-        <v>14264.1416</v>
+        <v>1458633.461598309</v>
       </c>
       <c r="F4" t="n">
-        <v>59507.79268292683</v>
+        <v>69021.50689905592</v>
       </c>
       <c r="G4" t="n">
-        <v>61945.24390243903</v>
+        <v>32592.23674655047</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1463414634146341</v>
+        <v>0.06463326071169208</v>
       </c>
     </row>
     <row r="5">
@@ -563,19 +563,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>116</v>
+        <v>904</v>
       </c>
       <c r="E5" t="n">
-        <v>19325.9765</v>
+        <v>895194.737665358</v>
       </c>
       <c r="F5" t="n">
-        <v>68678.03448275862</v>
+        <v>50413.69137168142</v>
       </c>
       <c r="G5" t="n">
-        <v>70501.12931034483</v>
+        <v>29202.21238938053</v>
       </c>
       <c r="H5" t="n">
-        <v>0.146551724137931</v>
+        <v>0.1703539823008849</v>
       </c>
     </row>
     <row r="6">
@@ -593,19 +593,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21</v>
+        <v>477</v>
       </c>
       <c r="E6" t="n">
-        <v>4063.403</v>
+        <v>482935.310602611</v>
       </c>
       <c r="F6" t="n">
-        <v>66610.19047619047</v>
+        <v>22106.0607966457</v>
       </c>
       <c r="G6" t="n">
-        <v>70847.42857142857</v>
+        <v>11444.65408805031</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09523809523809523</v>
+        <v>0.04821802935010482</v>
       </c>
     </row>
     <row r="7">
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>38</v>
+        <v>334</v>
       </c>
       <c r="E7" t="n">
-        <v>7383.8236</v>
+        <v>295415.431000268</v>
       </c>
       <c r="F7" t="n">
-        <v>67305</v>
+        <v>21146.07784431138</v>
       </c>
       <c r="G7" t="n">
-        <v>68787.97368421052</v>
+        <v>10612.87425149701</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.1616766467065868</v>
       </c>
     </row>
     <row r="8">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E8" t="n">
-        <v>1577.4327</v>
+        <v>86393.263556012</v>
       </c>
       <c r="F8" t="n">
-        <v>84772.25</v>
+        <v>57120.62105263158</v>
       </c>
       <c r="G8" t="n">
-        <v>88148.375</v>
+        <v>34095.47368421053</v>
       </c>
       <c r="H8" t="n">
-        <v>0.25</v>
+        <v>0.03157894736842105</v>
       </c>
     </row>
     <row r="9">
@@ -683,19 +683,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="E9" t="n">
-        <v>1122.8847</v>
+        <v>39337.480914004</v>
       </c>
       <c r="F9" t="n">
-        <v>93840.16666666667</v>
+        <v>43779.28846153846</v>
       </c>
       <c r="G9" t="n">
-        <v>97974.5</v>
+        <v>35628.84615384616</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1346153846153846</v>
       </c>
     </row>
     <row r="10">
@@ -713,19 +713,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>24</v>
+        <v>1788</v>
       </c>
       <c r="E10" t="n">
-        <v>4559.0589</v>
+        <v>1381869.90233174</v>
       </c>
       <c r="F10" t="n">
-        <v>74315.54166666667</v>
+        <v>38225.50055928412</v>
       </c>
       <c r="G10" t="n">
-        <v>76213.95833333333</v>
+        <v>15904.32158836689</v>
       </c>
       <c r="H10" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.03803131991051454</v>
       </c>
     </row>
     <row r="11">
@@ -743,19 +743,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>54</v>
+        <v>1932</v>
       </c>
       <c r="E11" t="n">
-        <v>8600.978999999999</v>
+        <v>1337572.70949007</v>
       </c>
       <c r="F11" t="n">
-        <v>75040.42592592593</v>
+        <v>24653.53157349896</v>
       </c>
       <c r="G11" t="n">
-        <v>75379.22222222222</v>
+        <v>12214.94099378882</v>
       </c>
       <c r="H11" t="n">
-        <v>0.09259259259259259</v>
+        <v>0.09679089026915114</v>
       </c>
     </row>
     <row r="12">
@@ -773,19 +773,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>71</v>
+        <v>1381</v>
       </c>
       <c r="E12" t="n">
-        <v>12108.2717</v>
+        <v>1477476.59094977</v>
       </c>
       <c r="F12" t="n">
-        <v>82766.94366197183</v>
+        <v>76971.06879073135</v>
       </c>
       <c r="G12" t="n">
-        <v>80984.60563380281</v>
+        <v>34082.33888486604</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1830985915492958</v>
+        <v>0.05503258508327299</v>
       </c>
     </row>
     <row r="13">
@@ -803,19 +803,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>106</v>
+        <v>950</v>
       </c>
       <c r="E13" t="n">
-        <v>18755.577</v>
+        <v>941528.6591029</v>
       </c>
       <c r="F13" t="n">
-        <v>62107.80188679245</v>
+        <v>57571.17263157895</v>
       </c>
       <c r="G13" t="n">
-        <v>63478.37735849056</v>
+        <v>30113.68421052632</v>
       </c>
       <c r="H13" t="n">
-        <v>0.08490566037735849</v>
+        <v>0.1326315789473684</v>
       </c>
     </row>
     <row r="14">
@@ -833,19 +833,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>481</v>
       </c>
       <c r="E14" t="n">
-        <v>6233.6818</v>
+        <v>471860.5128889</v>
       </c>
       <c r="F14" t="n">
-        <v>78515.36111111111</v>
+        <v>23522.93762993763</v>
       </c>
       <c r="G14" t="n">
-        <v>82644.66666666667</v>
+        <v>11572.05821205821</v>
       </c>
       <c r="H14" t="n">
-        <v>0.25</v>
+        <v>0.05613305613305614</v>
       </c>
     </row>
     <row r="15">
@@ -863,19 +863,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>44</v>
+        <v>322</v>
       </c>
       <c r="E15" t="n">
-        <v>7648.5877</v>
+        <v>271403.9850302</v>
       </c>
       <c r="F15" t="n">
-        <v>64773.61363636364</v>
+        <v>16460.63043478261</v>
       </c>
       <c r="G15" t="n">
-        <v>63440.52272727273</v>
+        <v>10888.50931677019</v>
       </c>
       <c r="H15" t="n">
-        <v>0.06818181818181818</v>
+        <v>0.1149068322981366</v>
       </c>
     </row>
     <row r="16">
@@ -893,19 +893,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="E16" t="n">
-        <v>2498.499</v>
+        <v>79586.18666940001</v>
       </c>
       <c r="F16" t="n">
-        <v>67475.30769230769</v>
+        <v>53197.04347826087</v>
       </c>
       <c r="G16" t="n">
-        <v>63481.61538461538</v>
+        <v>34301.63043478261</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.03260869565217391</v>
       </c>
     </row>
     <row r="17">
@@ -923,19 +923,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="E17" t="n">
-        <v>1208.329</v>
+        <v>52677.0729066</v>
       </c>
       <c r="F17" t="n">
-        <v>56735.16666666666</v>
+        <v>62405.96923076923</v>
       </c>
       <c r="G17" t="n">
-        <v>57964.16666666666</v>
+        <v>46460</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.1538461538461539</v>
       </c>
     </row>
   </sheetData>

--- a/sample_data/output/excel/03_주택종류별_집계.xlsx
+++ b/sample_data/output/excel/03_주택종류별_집계.xlsx
@@ -485,7 +485,7 @@
         <v>15548.62617924528</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04952830188679246</v>
+        <v>0.03773584905660377</v>
       </c>
     </row>
     <row r="3">
@@ -515,7 +515,7 @@
         <v>11724.16020236088</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09499718943226532</v>
+        <v>0.08487914558740865</v>
       </c>
     </row>
     <row r="4">
@@ -545,7 +545,7 @@
         <v>32592.23674655047</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06463326071169208</v>
+        <v>0.05591866376180102</v>
       </c>
     </row>
     <row r="5">
@@ -575,7 +575,7 @@
         <v>29202.21238938053</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1703539823008849</v>
+        <v>0.1526548672566372</v>
       </c>
     </row>
     <row r="6">
@@ -605,7 +605,7 @@
         <v>11444.65408805031</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04821802935010482</v>
+        <v>0.0440251572327044</v>
       </c>
     </row>
     <row r="7">
@@ -635,7 +635,7 @@
         <v>10612.87425149701</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1616766467065868</v>
+        <v>0.1437125748502994</v>
       </c>
     </row>
     <row r="8">
@@ -665,7 +665,7 @@
         <v>34095.47368421053</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03157894736842105</v>
+        <v>0.02105263157894737</v>
       </c>
     </row>
     <row r="9">
@@ -725,7 +725,7 @@
         <v>15904.32158836689</v>
       </c>
       <c r="H10" t="n">
-        <v>0.03803131991051454</v>
+        <v>0.03187919463087249</v>
       </c>
     </row>
     <row r="11">
@@ -755,7 +755,7 @@
         <v>12214.94099378882</v>
       </c>
       <c r="H11" t="n">
-        <v>0.09679089026915114</v>
+        <v>0.08695652173913043</v>
       </c>
     </row>
     <row r="12">
@@ -785,7 +785,7 @@
         <v>34082.33888486604</v>
       </c>
       <c r="H12" t="n">
-        <v>0.05503258508327299</v>
+        <v>0.05286024619840695</v>
       </c>
     </row>
     <row r="13">
@@ -815,7 +815,7 @@
         <v>30113.68421052632</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1326315789473684</v>
+        <v>0.1242105263157895</v>
       </c>
     </row>
     <row r="14">
@@ -845,7 +845,7 @@
         <v>11572.05821205821</v>
       </c>
       <c r="H14" t="n">
-        <v>0.05613305613305614</v>
+        <v>0.05197505197505198</v>
       </c>
     </row>
     <row r="15">
@@ -875,7 +875,7 @@
         <v>10888.50931677019</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1149068322981366</v>
+        <v>0.1024844720496894</v>
       </c>
     </row>
     <row r="16">
@@ -905,7 +905,7 @@
         <v>34301.63043478261</v>
       </c>
       <c r="H16" t="n">
-        <v>0.03260869565217391</v>
+        <v>0.02173913043478261</v>
       </c>
     </row>
     <row r="17">
@@ -935,7 +935,7 @@
         <v>46460</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1538461538461539</v>
+        <v>0.1384615384615385</v>
       </c>
     </row>
   </sheetData>
